--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260727.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260727.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.88%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.76%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>華碩電腦</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>5,688,000</t>
+          <t>5,820,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>華碩電腦</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,820,000</t>
+          <t>5,759,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>20,339,000</t>
+          <t>33,959,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -733,66 +733,66 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>33,959,000</t>
+          <t>20,339,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>9,544,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>9,544,000</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -814,46 +814,46 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>6,485,000</t>
+          <t>32,918,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>30,079,000</t>
+          <t>6,485,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,44 +865,44 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>32,918,000</t>
+          <t>24,881,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>24,881,000</t>
+          <t>30,079,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>4,096,000</t>
+          <t>4,126,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -975,44 +975,44 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>8,977,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>8,532,000</t>
+          <t>15,056,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -1041,176 +1041,176 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,151,000</t>
+          <t>32,659,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>32,659,000</t>
+          <t>2,151,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>3,862,000</t>
+          <t>17,369,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>17,369,000</t>
+          <t>3,862,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>2,619,035,808</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>8,904,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2,493,603,276</t>
+          <t>8,904,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -1298,117 +1298,117 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,666,000</t>
+          <t>3,498,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>5,666,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>23,205,000</t>
+          <t>518,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>3,334,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>518,000</t>
+          <t>23,205,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,994,865,322</t>
+          <t>2,002,785,322</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>6,870,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1591,22 +1591,22 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>6,553,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1672,46 +1672,46 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>17,290,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>17,290,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1761,6 +1761,28 @@
       <c r="D73" s="4" t="inlineStr">
         <is>
           <t>0.60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>PB_NTD</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>PAYABLES</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>-50,087,598</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
         </is>
       </c>
     </row>
